--- a/data/trans_bre/P16A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,66</t>
+          <t>1,43; 8,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,8</t>
+          <t>-2,08; 6,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 7,26</t>
+          <t>-0,46; 7,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,19</t>
+          <t>-1,27; 3,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,93; 796,68</t>
+          <t>24,25; 665,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 169,56</t>
+          <t>-27,24; 152,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 352,24</t>
+          <t>-11,88; 358,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 230,87</t>
+          <t>-33,01; 280,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,97</t>
+          <t>1,78; 6,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,99</t>
+          <t>1,52; 8,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,05</t>
+          <t>1,11; 6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,8</t>
+          <t>0,34; 6,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,12; 505,25</t>
+          <t>41,49; 455,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 367,47</t>
+          <t>17,72; 351,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 338,95</t>
+          <t>25,18; 338,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 154,36</t>
+          <t>0,65; 147,69</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; -0,37</t>
+          <t>-3,65; -0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,13</t>
+          <t>-4,93; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,74</t>
+          <t>-0,37; 5,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,16</t>
+          <t>-0,03; 6,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,44; 67,38</t>
+          <t>-77,35; 81,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 347,66</t>
+          <t>-12,64; 366,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 194,9</t>
+          <t>-3,09; 192,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,18</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,83</t>
+          <t>4,71; 11,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,1</t>
+          <t>0,38; 7,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,85</t>
+          <t>-2,3; 3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 998,82</t>
+          <t>6,93; 1146,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,49; 1038,74</t>
+          <t>110,15; 1010,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 303,1</t>
+          <t>2,86; 276,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 252,32</t>
+          <t>-52,31; 277,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 7,21</t>
+          <t>0,05; 7,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 17,8</t>
+          <t>6,71; 17,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 14,08</t>
+          <t>3,33; 14,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,78</t>
+          <t>4,86; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 683,78</t>
+          <t>-9,78; 770,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,58; 884,13</t>
+          <t>98,72; 911,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,14; 523,69</t>
+          <t>42,76; 576,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,98; 751,05</t>
+          <t>99,69; 695,72</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,49</t>
+          <t>0,48; 5,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,45</t>
+          <t>-0,36; 6,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,86</t>
+          <t>-1,14; 5,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,0</t>
+          <t>2,13; 8,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,36; —</t>
+          <t>-39,58; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 453,03</t>
+          <t>-21,05; 463,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 334,79</t>
+          <t>-32,1; 341,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,82; 254,09</t>
+          <t>26,29; 246,01</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,66</t>
+          <t>0,28; 4,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,22</t>
+          <t>-0,98; 3,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,21</t>
+          <t>1,41; 6,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,14</t>
+          <t>-0,71; 6,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 264,95</t>
+          <t>4,72; 242,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 163,99</t>
+          <t>-25,66; 158,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,06; 259,53</t>
+          <t>25,03; 256,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 194,69</t>
+          <t>-13,83; 197,54</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,74</t>
+          <t>0,72; 5,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,73</t>
+          <t>2,18; 6,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,41</t>
+          <t>2,84; 7,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,01</t>
+          <t>4,56; 10,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,36; 170,26</t>
+          <t>12,91; 160,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,77; 353,98</t>
+          <t>49,3; 373,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,69; 310,89</t>
+          <t>69,78; 336,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,35; 493,02</t>
+          <t>78,58; 506,67</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,67</t>
+          <t>1,74; 3,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,76</t>
+          <t>2,59; 4,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,35</t>
+          <t>3,09; 5,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,17</t>
+          <t>2,32; 5,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57,93; 164,74</t>
+          <t>58,49; 167,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,66; 167,26</t>
+          <t>67,08; 171,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,32; 173,45</t>
+          <t>76,87; 174,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54,4; 155,71</t>
+          <t>52,4; 157,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,6</t>
+          <t>1,4; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,33</t>
+          <t>-2,73; 6,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 7,29</t>
+          <t>-0,68; 7,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,64</t>
+          <t>-1,28; 3,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,25; 665,06</t>
+          <t>25,94; 662,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 152,54</t>
+          <t>-33,61; 174,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 358,9</t>
+          <t>-18,79; 374,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 280,89</t>
+          <t>-33,04; 234,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,85</t>
+          <t>1,75; 6,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,09</t>
+          <t>1,22; 7,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,92</t>
+          <t>0,84; 6,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,66</t>
+          <t>0,33; 6,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,49; 455,83</t>
+          <t>41,46; 441,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 351,8</t>
+          <t>15,83; 342,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 338,78</t>
+          <t>15,92; 298,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 147,69</t>
+          <t>3,61; 145,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,35</t>
+          <t>-3,63; -0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1,39</t>
+          <t>-4,66; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,84</t>
+          <t>-0,62; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,17</t>
+          <t>-0,04; 5,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 36,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,35; 81,95</t>
+          <t>-80,04; 66,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 366,09</t>
+          <t>-18,88; 314,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 192,69</t>
+          <t>-1,74; 206,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,3; 5,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,84</t>
+          <t>4,45; 11,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,96</t>
+          <t>0,77; 7,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,01</t>
+          <t>-1,06; 4,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 1146,45</t>
+          <t>-15,26; 1142,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>110,15; 1010,1</t>
+          <t>91,39; 1050,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 276,49</t>
+          <t>5,21; 252,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 277,83</t>
+          <t>-36,5; 486,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,8</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>291,16%</t>
+          <t>311,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,51</t>
+          <t>-0,02; 7,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 17,95</t>
+          <t>5,85; 17,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,62</t>
+          <t>3,27; 14,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,81</t>
+          <t>4,57; 10,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 770,33</t>
+          <t>-21,17; 882,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>98,72; 911,15</t>
+          <t>73,83; 838,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,76; 576,33</t>
+          <t>42,75; 560,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>99,69; 695,72</t>
+          <t>104,82; 817,47</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>108,95%</t>
+          <t>112,57%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,36</t>
+          <t>0,51; 5,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,39</t>
+          <t>-0,21; 6,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,66</t>
+          <t>-1,45; 5,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,96</t>
+          <t>2,36; 9,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,58; —</t>
+          <t>-10,26; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 463,84</t>
+          <t>-17,68; 491,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 341,4</t>
+          <t>-39,05; 370,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,29; 246,01</t>
+          <t>26,6; 257,17</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>5,31</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>139,44%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,38</t>
+          <t>0,43; 4,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,26</t>
+          <t>-1,19; 3,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,46</t>
+          <t>1,13; 6,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,46</t>
+          <t>2,93; 7,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 242,22</t>
+          <t>6,08; 247,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 158,51</t>
+          <t>-30,08; 149,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,03; 256,63</t>
+          <t>19,87; 234,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 197,54</t>
+          <t>57,82; 268,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>180,18%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,65</t>
+          <t>0,49; 5,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,84</t>
+          <t>2,26; 6,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,61</t>
+          <t>2,9; 7,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,35</t>
+          <t>3,04; 7,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,91; 160,88</t>
+          <t>7,19; 159,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,3; 373,49</t>
+          <t>58,15; 371,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,78; 336,97</t>
+          <t>65,37; 326,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,58; 506,67</t>
+          <t>46,16; 177,79</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,64</t>
+          <t>1,76; 3,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,86</t>
+          <t>2,68; 4,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,34</t>
+          <t>3,05; 5,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,26</t>
+          <t>3,11; 5,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,49; 167,3</t>
+          <t>58,07; 164,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,08; 171,7</t>
+          <t>67,04; 166,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,87; 174,9</t>
+          <t>77,07; 173,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>52,4; 157,61</t>
+          <t>65,43; 137,06</t>
         </is>
       </c>
     </row>
